--- a/GastosAndre.xlsx
+++ b/GastosAndre.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Nome</t>
   </si>
@@ -37,6 +37,15 @@
   </si>
   <si>
     <t>gasolina</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>ifood</t>
+  </si>
+  <si>
+    <t>açai</t>
   </si>
 </sst>
 </file>
@@ -409,28 +418,60 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>750</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46179</v>
+      </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46183</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>200</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46193</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46203</v>
+      </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
